--- a/backend/helpers/db_seeder/data/role_uprawnienia.xlsx
+++ b/backend/helpers/db_seeder/data/role_uprawnienia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kompetencyjny\Smart-University-Scheduler\helpers\db_seeder\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Smart-University-Scheduler\helpers\db_seeder\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F317874-4BC0-4E7B-B789-C2FB1D819C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8ED8031-B46D-49E0-B168-972FBA6C8EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="208">
   <si>
     <t>Uprawnienie \ Rola</t>
   </si>
@@ -690,6 +690,12 @@
   </si>
   <si>
     <t>custom-events:create</t>
+  </si>
+  <si>
+    <t>api key</t>
+  </si>
+  <si>
+    <t>api-key:generate</t>
   </si>
 </sst>
 </file>
@@ -1042,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K157"/>
+  <dimension ref="A1:K158"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
@@ -4269,46 +4275,48 @@
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="4"/>
+      <c r="B103" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C103" t="s">
+        <v>207</v>
+      </c>
+      <c r="D103">
+        <v>1</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A104" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B104" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C103" s="2" t="s">
+      <c r="C104" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D103">
-        <v>1</v>
-      </c>
-      <c r="E103">
-        <v>1</v>
-      </c>
-      <c r="F103">
-        <v>1</v>
-      </c>
-      <c r="G103">
-        <v>0</v>
-      </c>
-      <c r="H103">
-        <v>0</v>
-      </c>
-      <c r="I103">
-        <v>0</v>
-      </c>
-      <c r="J103">
-        <v>0</v>
-      </c>
-      <c r="K103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A104" s="4"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="D104">
         <v>1</v>
       </c>
@@ -4319,26 +4327,26 @@
         <v>1</v>
       </c>
       <c r="G104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="2" t="s">
-        <v>194</v>
+        <v>135</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -4356,20 +4364,20 @@
         <v>1</v>
       </c>
       <c r="I105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="2" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -4387,20 +4395,20 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K106">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -4412,26 +4420,26 @@
         <v>1</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -4462,7 +4470,7 @@
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -4474,96 +4482,96 @@
         <v>1</v>
       </c>
       <c r="G109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K109">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="2" t="s">
-        <v>200</v>
+        <v>139</v>
       </c>
       <c r="D110">
         <v>1</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="4"/>
-      <c r="B111" s="4" t="s">
-        <v>140</v>
-      </c>
+      <c r="B111" s="4"/>
       <c r="C111" s="2" t="s">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="D111">
         <v>1</v>
       </c>
       <c r="E111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K111">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="4"/>
-      <c r="B112" s="4"/>
+      <c r="B112" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="C112" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D112">
         <v>1</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -4572,23 +4580,23 @@
         <v>1</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -4617,17 +4625,15 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="4"/>
-      <c r="B114" s="4" t="s">
-        <v>144</v>
-      </c>
+      <c r="B114" s="4"/>
       <c r="C114" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D114">
         <v>1</v>
       </c>
       <c r="E114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114">
         <v>1</v>
@@ -4636,23 +4642,25 @@
         <v>1</v>
       </c>
       <c r="H114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K114">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="4"/>
-      <c r="B115" s="4"/>
+      <c r="B115" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="C115" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -4683,7 +4691,7 @@
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -4695,26 +4703,26 @@
         <v>1</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -4745,7 +4753,7 @@
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D118">
         <v>1</v>
@@ -4774,11 +4782,9 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="4"/>
-      <c r="B119" s="4" t="s">
-        <v>150</v>
-      </c>
+      <c r="B119" s="4"/>
       <c r="C119" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -4790,16 +4796,16 @@
         <v>1</v>
       </c>
       <c r="G119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K119">
         <v>0</v>
@@ -4807,9 +4813,11 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" s="4"/>
-      <c r="B120" s="4"/>
+      <c r="B120" s="4" t="s">
+        <v>150</v>
+      </c>
       <c r="C120" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -4840,7 +4848,7 @@
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -4871,7 +4879,7 @@
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -4883,16 +4891,16 @@
         <v>1</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K122">
         <v>0</v>
@@ -4902,7 +4910,7 @@
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -4933,7 +4941,7 @@
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -4964,7 +4972,7 @@
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -4993,11 +5001,9 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" s="4"/>
-      <c r="B126" s="4" t="s">
-        <v>158</v>
-      </c>
+      <c r="B126" s="4"/>
       <c r="C126" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -5009,16 +5015,16 @@
         <v>1</v>
       </c>
       <c r="G126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K126">
         <v>0</v>
@@ -5026,9 +5032,11 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" s="4"/>
-      <c r="B127" s="4"/>
+      <c r="B127" s="4" t="s">
+        <v>158</v>
+      </c>
       <c r="C127" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -5059,13 +5067,13 @@
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D128">
         <v>1</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -5077,10 +5085,10 @@
         <v>1</v>
       </c>
       <c r="I128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128">
         <v>0</v>
@@ -5090,7 +5098,7 @@
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -5121,7 +5129,7 @@
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -5133,10 +5141,10 @@
         <v>1</v>
       </c>
       <c r="G130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130">
         <v>0</v>
@@ -5150,17 +5158,15 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="4"/>
-      <c r="B131" s="4" t="s">
-        <v>201</v>
-      </c>
+      <c r="B131" s="4"/>
       <c r="C131" s="2" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="D131">
         <v>1</v>
       </c>
       <c r="E131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -5183,9 +5189,11 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="4"/>
-      <c r="B132" s="4"/>
+      <c r="B132" s="4" t="s">
+        <v>201</v>
+      </c>
       <c r="C132" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -5197,16 +5205,16 @@
         <v>1</v>
       </c>
       <c r="G132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -5216,7 +5224,7 @@
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -5228,16 +5236,16 @@
         <v>1</v>
       </c>
       <c r="G133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133">
         <v>0</v>
@@ -5247,73 +5255,73 @@
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D134">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>1</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A135" s="4"/>
+      <c r="B135" s="4"/>
+      <c r="C135" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D134">
-        <v>1</v>
-      </c>
-      <c r="E134">
-        <v>1</v>
-      </c>
-      <c r="F134">
-        <v>1</v>
-      </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-      <c r="H134">
-        <v>0</v>
-      </c>
-      <c r="I134">
-        <v>0</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A135" s="4" t="s">
+      <c r="D135">
+        <v>1</v>
+      </c>
+      <c r="E135">
+        <v>1</v>
+      </c>
+      <c r="F135">
+        <v>1</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B136" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C135" t="s">
+      <c r="C136" t="s">
         <v>166</v>
-      </c>
-      <c r="D135">
-        <v>1</v>
-      </c>
-      <c r="E135">
-        <v>0</v>
-      </c>
-      <c r="F135">
-        <v>0</v>
-      </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A136" s="4"/>
-      <c r="B136" s="4"/>
-      <c r="C136" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -5344,73 +5352,73 @@
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D137">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>0</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A138" s="4"/>
+      <c r="B138" s="4"/>
+      <c r="C138" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D137">
-        <v>1</v>
-      </c>
-      <c r="E137">
-        <v>0</v>
-      </c>
-      <c r="F137">
-        <v>0</v>
-      </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A138" s="4" t="s">
+      <c r="D138">
+        <v>1</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A139" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B139" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C139" t="s">
         <v>170</v>
-      </c>
-      <c r="D138">
-        <v>1</v>
-      </c>
-      <c r="E138">
-        <v>0</v>
-      </c>
-      <c r="F138">
-        <v>0</v>
-      </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A139" s="4"/>
-      <c r="B139" s="4"/>
-      <c r="C139" t="s">
-        <v>171</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -5441,7 +5449,7 @@
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -5472,7 +5480,7 @@
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -5503,7 +5511,7 @@
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -5534,73 +5542,73 @@
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" t="s">
+        <v>174</v>
+      </c>
+      <c r="D143">
+        <v>1</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A144" s="4"/>
+      <c r="B144" s="4"/>
+      <c r="C144" t="s">
         <v>175</v>
       </c>
-      <c r="D143">
-        <v>1</v>
-      </c>
-      <c r="E143">
-        <v>0</v>
-      </c>
-      <c r="F143">
-        <v>0</v>
-      </c>
-      <c r="G143">
-        <v>0</v>
-      </c>
-      <c r="H143">
-        <v>0</v>
-      </c>
-      <c r="I143">
-        <v>0</v>
-      </c>
-      <c r="J143">
-        <v>0</v>
-      </c>
-      <c r="K143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A144" s="4" t="s">
+      <c r="D144">
+        <v>1</v>
+      </c>
+      <c r="E144">
+        <v>0</v>
+      </c>
+      <c r="F144">
+        <v>0</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A145" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B145" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C145" t="s">
         <v>178</v>
-      </c>
-      <c r="D144">
-        <v>1</v>
-      </c>
-      <c r="E144">
-        <v>1</v>
-      </c>
-      <c r="F144">
-        <v>1</v>
-      </c>
-      <c r="G144">
-        <v>1</v>
-      </c>
-      <c r="H144">
-        <v>1</v>
-      </c>
-      <c r="I144">
-        <v>1</v>
-      </c>
-      <c r="J144">
-        <v>0</v>
-      </c>
-      <c r="K144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A145" s="4"/>
-      <c r="B145" s="4"/>
-      <c r="C145" t="s">
-        <v>179</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -5631,7 +5639,7 @@
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -5662,7 +5670,7 @@
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -5693,7 +5701,7 @@
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -5722,11 +5730,9 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="4"/>
-      <c r="B149" s="4" t="s">
-        <v>183</v>
-      </c>
+      <c r="B149" s="4"/>
       <c r="C149" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -5755,111 +5761,113 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="4"/>
-      <c r="B150" s="4"/>
+      <c r="B150" s="4" t="s">
+        <v>183</v>
+      </c>
       <c r="C150" t="s">
+        <v>184</v>
+      </c>
+      <c r="D150">
+        <v>1</v>
+      </c>
+      <c r="E150">
+        <v>1</v>
+      </c>
+      <c r="F150">
+        <v>1</v>
+      </c>
+      <c r="G150">
+        <v>1</v>
+      </c>
+      <c r="H150">
+        <v>1</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A151" s="4"/>
+      <c r="B151" s="4"/>
+      <c r="C151" t="s">
         <v>185</v>
       </c>
-      <c r="D150">
-        <v>1</v>
-      </c>
-      <c r="E150">
-        <v>1</v>
-      </c>
-      <c r="F150">
-        <v>1</v>
-      </c>
-      <c r="G150">
-        <v>1</v>
-      </c>
-      <c r="H150">
-        <v>1</v>
-      </c>
-      <c r="I150">
-        <v>1</v>
-      </c>
-      <c r="J150">
-        <v>0</v>
-      </c>
-      <c r="K150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A151" s="1" t="s">
+      <c r="D151">
+        <v>1</v>
+      </c>
+      <c r="E151">
+        <v>1</v>
+      </c>
+      <c r="F151">
+        <v>1</v>
+      </c>
+      <c r="G151">
+        <v>1</v>
+      </c>
+      <c r="H151">
+        <v>1</v>
+      </c>
+      <c r="I151">
+        <v>1</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B152" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C152" t="s">
         <v>186</v>
       </c>
-      <c r="D151">
-        <v>1</v>
-      </c>
-      <c r="E151">
-        <v>1</v>
-      </c>
-      <c r="F151">
-        <v>1</v>
-      </c>
-      <c r="G151">
-        <v>1</v>
-      </c>
-      <c r="H151">
-        <v>1</v>
-      </c>
-      <c r="I151">
-        <v>1</v>
-      </c>
-      <c r="J151">
-        <v>1</v>
-      </c>
-      <c r="K151">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A152" s="4" t="s">
+      <c r="D152">
+        <v>1</v>
+      </c>
+      <c r="E152">
+        <v>1</v>
+      </c>
+      <c r="F152">
+        <v>1</v>
+      </c>
+      <c r="G152">
+        <v>1</v>
+      </c>
+      <c r="H152">
+        <v>1</v>
+      </c>
+      <c r="I152">
+        <v>1</v>
+      </c>
+      <c r="J152">
+        <v>1</v>
+      </c>
+      <c r="K152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A153" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B153" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C153" t="s">
         <v>190</v>
       </c>
-      <c r="D152">
-        <v>1</v>
-      </c>
-      <c r="E152">
-        <v>1</v>
-      </c>
-      <c r="F152">
-        <v>0</v>
-      </c>
-      <c r="G152">
-        <v>0</v>
-      </c>
-      <c r="H152">
-        <v>0</v>
-      </c>
-      <c r="I152">
-        <v>0</v>
-      </c>
-      <c r="J152">
-        <v>0</v>
-      </c>
-      <c r="K152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A153" s="4"/>
-      <c r="B153" s="4"/>
-      <c r="C153" t="s">
-        <v>191</v>
-      </c>
       <c r="D153">
         <v>1</v>
       </c>
@@ -5867,13 +5875,13 @@
         <v>1</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I153">
         <v>0</v>
@@ -5889,7 +5897,7 @@
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D154">
         <v>1</v>
@@ -5898,13 +5906,13 @@
         <v>1</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154">
         <v>0</v>
@@ -5920,108 +5928,138 @@
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" t="s">
+        <v>192</v>
+      </c>
+      <c r="D155">
+        <v>1</v>
+      </c>
+      <c r="E155">
+        <v>1</v>
+      </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A156" s="4"/>
+      <c r="B156" s="4"/>
+      <c r="C156" t="s">
         <v>193</v>
       </c>
-      <c r="D155">
-        <v>1</v>
-      </c>
-      <c r="E155">
-        <v>1</v>
-      </c>
-      <c r="F155">
-        <v>0</v>
-      </c>
-      <c r="G155">
-        <v>0</v>
-      </c>
-      <c r="H155">
-        <v>0</v>
-      </c>
-      <c r="I155">
-        <v>0</v>
-      </c>
-      <c r="J155">
-        <v>0</v>
-      </c>
-      <c r="K155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A156" s="4" t="s">
+      <c r="D156">
+        <v>1</v>
+      </c>
+      <c r="E156">
+        <v>1</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A157" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="B157" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="C156" t="s">
+      <c r="C157" t="s">
         <v>197</v>
       </c>
-      <c r="D156">
-        <v>1</v>
-      </c>
-      <c r="E156">
-        <v>1</v>
-      </c>
-      <c r="F156">
-        <v>0</v>
-      </c>
-      <c r="G156">
-        <v>0</v>
-      </c>
-      <c r="H156">
-        <v>0</v>
-      </c>
-      <c r="I156">
-        <v>0</v>
-      </c>
-      <c r="J156">
-        <v>0</v>
-      </c>
-      <c r="K156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A157" s="4"/>
-      <c r="B157" s="4"/>
-      <c r="C157" t="s">
+      <c r="D157">
+        <v>1</v>
+      </c>
+      <c r="E157">
+        <v>1</v>
+      </c>
+      <c r="F157">
+        <v>0</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A158" s="4"/>
+      <c r="B158" s="4"/>
+      <c r="C158" t="s">
         <v>198</v>
       </c>
-      <c r="D157">
-        <v>1</v>
-      </c>
-      <c r="E157">
-        <v>1</v>
-      </c>
-      <c r="F157">
-        <v>0</v>
-      </c>
-      <c r="G157">
-        <v>0</v>
-      </c>
-      <c r="H157">
-        <v>0</v>
-      </c>
-      <c r="I157">
-        <v>0</v>
-      </c>
-      <c r="J157">
-        <v>0</v>
-      </c>
-      <c r="K157">
+      <c r="D158">
+        <v>1</v>
+      </c>
+      <c r="E158">
+        <v>1</v>
+      </c>
+      <c r="F158">
+        <v>0</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="B156:B157"/>
+    <mergeCell ref="A157:A158"/>
+    <mergeCell ref="B157:B158"/>
     <mergeCell ref="B32:B36"/>
     <mergeCell ref="B37:B41"/>
     <mergeCell ref="B42:B46"/>
     <mergeCell ref="A67:A86"/>
-    <mergeCell ref="A87:A102"/>
     <mergeCell ref="B67:B71"/>
     <mergeCell ref="B72:B76"/>
     <mergeCell ref="B77:B81"/>
@@ -6029,10 +6067,10 @@
     <mergeCell ref="B87:B92"/>
     <mergeCell ref="B93:B97"/>
     <mergeCell ref="B98:B102"/>
-    <mergeCell ref="A152:A155"/>
-    <mergeCell ref="B152:B155"/>
-    <mergeCell ref="B103:B110"/>
-    <mergeCell ref="A103:A134"/>
+    <mergeCell ref="A153:A156"/>
+    <mergeCell ref="B153:B156"/>
+    <mergeCell ref="B104:B111"/>
+    <mergeCell ref="A104:A135"/>
     <mergeCell ref="A2:A26"/>
     <mergeCell ref="A27:A66"/>
     <mergeCell ref="B2:B6"/>
@@ -6045,18 +6083,19 @@
     <mergeCell ref="B52:B56"/>
     <mergeCell ref="B57:B61"/>
     <mergeCell ref="B62:B66"/>
-    <mergeCell ref="B131:B134"/>
-    <mergeCell ref="A135:A137"/>
-    <mergeCell ref="A138:A143"/>
-    <mergeCell ref="A144:A150"/>
-    <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B114:B118"/>
-    <mergeCell ref="B119:B125"/>
-    <mergeCell ref="B126:B130"/>
-    <mergeCell ref="B135:B137"/>
-    <mergeCell ref="B138:B143"/>
-    <mergeCell ref="B144:B148"/>
-    <mergeCell ref="B149:B150"/>
+    <mergeCell ref="B132:B135"/>
+    <mergeCell ref="A87:A103"/>
+    <mergeCell ref="A136:A138"/>
+    <mergeCell ref="A139:A144"/>
+    <mergeCell ref="A145:A151"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="B115:B119"/>
+    <mergeCell ref="B120:B126"/>
+    <mergeCell ref="B127:B131"/>
+    <mergeCell ref="B136:B138"/>
+    <mergeCell ref="B139:B144"/>
+    <mergeCell ref="B145:B149"/>
+    <mergeCell ref="B150:B151"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/backend/helpers/db_seeder/data/role_uprawnienia.xlsx
+++ b/backend/helpers/db_seeder/data/role_uprawnienia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Smart-University-Scheduler\helpers\db_seeder\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Studia\semestr6\Projekt_kompetencyjny\Smart-University-Scheduler\helpers\db_seeder\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8ED8031-B46D-49E0-B168-972FBA6C8EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B2B3B9-CCC1-45D4-A9A7-97FCF39D07A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4835,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="I120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120">
         <v>1</v>
@@ -4866,7 +4866,7 @@
         <v>1</v>
       </c>
       <c r="I121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121">
         <v>1</v>
@@ -6054,6 +6054,32 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="A136:A138"/>
+    <mergeCell ref="A139:A144"/>
+    <mergeCell ref="A145:A151"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="B115:B119"/>
+    <mergeCell ref="B120:B126"/>
+    <mergeCell ref="B127:B131"/>
+    <mergeCell ref="B136:B138"/>
+    <mergeCell ref="B139:B144"/>
+    <mergeCell ref="B145:B149"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="A104:A135"/>
+    <mergeCell ref="A2:A26"/>
+    <mergeCell ref="A27:A66"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="B52:B56"/>
+    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="B62:B66"/>
+    <mergeCell ref="B132:B135"/>
+    <mergeCell ref="A87:A103"/>
     <mergeCell ref="A157:A158"/>
     <mergeCell ref="B157:B158"/>
     <mergeCell ref="B32:B36"/>
@@ -6070,32 +6096,6 @@
     <mergeCell ref="A153:A156"/>
     <mergeCell ref="B153:B156"/>
     <mergeCell ref="B104:B111"/>
-    <mergeCell ref="A104:A135"/>
-    <mergeCell ref="A2:A26"/>
-    <mergeCell ref="A27:A66"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="B52:B56"/>
-    <mergeCell ref="B57:B61"/>
-    <mergeCell ref="B62:B66"/>
-    <mergeCell ref="B132:B135"/>
-    <mergeCell ref="A87:A103"/>
-    <mergeCell ref="A136:A138"/>
-    <mergeCell ref="A139:A144"/>
-    <mergeCell ref="A145:A151"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="B115:B119"/>
-    <mergeCell ref="B120:B126"/>
-    <mergeCell ref="B127:B131"/>
-    <mergeCell ref="B136:B138"/>
-    <mergeCell ref="B139:B144"/>
-    <mergeCell ref="B145:B149"/>
-    <mergeCell ref="B150:B151"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6104,14 +6104,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="36e2ff40-ab52-4240-babf-7476b65fdfdc">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="d3830623-0ee5-4634-96e5-1fabe66116f4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6304,21 +6302,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="36e2ff40-ab52-4240-babf-7476b65fdfdc">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="d3830623-0ee5-4634-96e5-1fabe66116f4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8710C31-AC30-4E45-B8BB-6B8E8A833604}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{650941DE-E334-4AB5-BCE8-14AB52A4A807}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="36e2ff40-ab52-4240-babf-7476b65fdfdc"/>
-    <ds:schemaRef ds:uri="d3830623-0ee5-4634-96e5-1fabe66116f4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6343,9 +6340,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{650941DE-E334-4AB5-BCE8-14AB52A4A807}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8710C31-AC30-4E45-B8BB-6B8E8A833604}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="36e2ff40-ab52-4240-babf-7476b65fdfdc"/>
+    <ds:schemaRef ds:uri="d3830623-0ee5-4634-96e5-1fabe66116f4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>